--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129996509</v>
       </c>
       <c r="B2" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,1825 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130041545</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475757</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6831512</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130041507</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>475660</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6831685</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130041431</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>475759</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6831598</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130041550</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>475670</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6831719</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130041549</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>475670</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6831652</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130041551</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>475733</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6831737</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130041445</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79119</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>475693</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831717</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130041547</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>475696</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6831636</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130041546</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>475705</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6831611</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130041552</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>475809</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6831753</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130041556</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>475656</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6831611</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130041444</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79119</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>185</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>475670</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6831719</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130041434</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>475658</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6831667</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130041491</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>475660</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6831683</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130041479</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79111</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>475670</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6831652</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130041490</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>475696</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831627</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130041548</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>475672</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831646</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129996509</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130041545</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130041507</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130041431</v>
       </c>
       <c r="B5" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130041550</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130041549</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041551</v>
+        <v>130041445</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475733</v>
+        <v>475693</v>
       </c>
       <c r="R8" t="n">
-        <v>6831737</v>
+        <v>6831717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041445</v>
+        <v>130041551</v>
       </c>
       <c r="B9" t="n">
-        <v>79119</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475693</v>
+        <v>475733</v>
       </c>
       <c r="R9" t="n">
-        <v>6831717</v>
+        <v>6831737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>130041547</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130041546</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130041552</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041556</v>
+        <v>130041444</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475656</v>
+        <v>475670</v>
       </c>
       <c r="R13" t="n">
-        <v>6831611</v>
+        <v>6831719</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041444</v>
+        <v>130041556</v>
       </c>
       <c r="B14" t="n">
-        <v>79119</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475670</v>
+        <v>475656</v>
       </c>
       <c r="R14" t="n">
-        <v>6831719</v>
+        <v>6831611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>130041434</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041491</v>
+        <v>130041479</v>
       </c>
       <c r="B16" t="n">
-        <v>78845</v>
+        <v>79112</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475660</v>
+        <v>475670</v>
       </c>
       <c r="R16" t="n">
-        <v>6831683</v>
+        <v>6831652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041479</v>
+        <v>130041491</v>
       </c>
       <c r="B17" t="n">
-        <v>79111</v>
+        <v>78846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475670</v>
+        <v>475660</v>
       </c>
       <c r="R17" t="n">
-        <v>6831652</v>
+        <v>6831683</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>130041490</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130041548</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,6 +2598,309 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130044577</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>475722</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6831725</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130044578</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79678</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>475722</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6831725</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130044580</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>475722</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6831725</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041445</v>
+        <v>130041551</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475693</v>
+        <v>475733</v>
       </c>
       <c r="R8" t="n">
-        <v>6831717</v>
+        <v>6831737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041551</v>
+        <v>130041547</v>
       </c>
       <c r="B9" t="n">
         <v>79088</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475733</v>
+        <v>475696</v>
       </c>
       <c r="R9" t="n">
-        <v>6831737</v>
+        <v>6831636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041547</v>
+        <v>130041445</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475696</v>
+        <v>475693</v>
       </c>
       <c r="R10" t="n">
-        <v>6831636</v>
+        <v>6831717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041551</v>
+        <v>130041445</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475733</v>
+        <v>475693</v>
       </c>
       <c r="R8" t="n">
-        <v>6831737</v>
+        <v>6831717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041547</v>
+        <v>130041551</v>
       </c>
       <c r="B9" t="n">
         <v>79088</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475696</v>
+        <v>475733</v>
       </c>
       <c r="R9" t="n">
-        <v>6831636</v>
+        <v>6831737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041445</v>
+        <v>130041547</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475693</v>
+        <v>475696</v>
       </c>
       <c r="R10" t="n">
-        <v>6831717</v>
+        <v>6831636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129996509</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130041545</v>
+        <v>130041507</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475757</v>
+        <v>475660</v>
       </c>
       <c r="R3" t="n">
-        <v>6831512</v>
+        <v>6831685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041507</v>
+        <v>130041431</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475660</v>
+        <v>475759</v>
       </c>
       <c r="R4" t="n">
-        <v>6831685</v>
+        <v>6831598</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041431</v>
+        <v>130041545</v>
       </c>
       <c r="B5" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475759</v>
+        <v>475757</v>
       </c>
       <c r="R5" t="n">
-        <v>6831598</v>
+        <v>6831512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>130041550</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130041549</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041445</v>
+        <v>130041551</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475693</v>
+        <v>475733</v>
       </c>
       <c r="R8" t="n">
-        <v>6831717</v>
+        <v>6831737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041551</v>
+        <v>130041547</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475733</v>
+        <v>475696</v>
       </c>
       <c r="R9" t="n">
-        <v>6831737</v>
+        <v>6831636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041547</v>
+        <v>130041445</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475696</v>
+        <v>475693</v>
       </c>
       <c r="R10" t="n">
-        <v>6831636</v>
+        <v>6831717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
         <v>130041546</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130041552</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130041444</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130041556</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>130041434</v>
       </c>
       <c r="B15" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041479</v>
+        <v>130041491</v>
       </c>
       <c r="B16" t="n">
-        <v>79112</v>
+        <v>78847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475670</v>
+        <v>475660</v>
       </c>
       <c r="R16" t="n">
-        <v>6831652</v>
+        <v>6831683</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041491</v>
+        <v>130041479</v>
       </c>
       <c r="B17" t="n">
-        <v>78846</v>
+        <v>79113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475660</v>
+        <v>475670</v>
       </c>
       <c r="R17" t="n">
-        <v>6831683</v>
+        <v>6831652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>130041490</v>
       </c>
       <c r="B18" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130041548</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>130044577</v>
       </c>
       <c r="B20" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>130044578</v>
       </c>
       <c r="B21" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>130044580</v>
       </c>
       <c r="B22" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041444</v>
+        <v>130041556</v>
       </c>
       <c r="B13" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475670</v>
+        <v>475656</v>
       </c>
       <c r="R13" t="n">
-        <v>6831719</v>
+        <v>6831611</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041556</v>
+        <v>130041444</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475656</v>
+        <v>475670</v>
       </c>
       <c r="R14" t="n">
-        <v>6831611</v>
+        <v>6831719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130041545</v>
+        <v>130041431</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475757</v>
+        <v>475759</v>
       </c>
       <c r="R3" t="n">
-        <v>6831512</v>
+        <v>6831598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041431</v>
+        <v>130041545</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475759</v>
+        <v>475757</v>
       </c>
       <c r="R5" t="n">
-        <v>6831598</v>
+        <v>6831512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041551</v>
+        <v>130041445</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475733</v>
+        <v>475693</v>
       </c>
       <c r="R8" t="n">
-        <v>6831737</v>
+        <v>6831717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041547</v>
+        <v>130041551</v>
       </c>
       <c r="B9" t="n">
         <v>79095</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475696</v>
+        <v>475733</v>
       </c>
       <c r="R9" t="n">
-        <v>6831636</v>
+        <v>6831737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041445</v>
+        <v>130041547</v>
       </c>
       <c r="B10" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475693</v>
+        <v>475696</v>
       </c>
       <c r="R10" t="n">
-        <v>6831717</v>
+        <v>6831636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041556</v>
+        <v>130041444</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475656</v>
+        <v>475670</v>
       </c>
       <c r="R13" t="n">
-        <v>6831611</v>
+        <v>6831719</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041444</v>
+        <v>130041556</v>
       </c>
       <c r="B14" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475670</v>
+        <v>475656</v>
       </c>
       <c r="R14" t="n">
-        <v>6831719</v>
+        <v>6831611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129996509</v>
       </c>
       <c r="B2" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130041431</v>
+        <v>130041545</v>
       </c>
       <c r="B3" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475759</v>
+        <v>475757</v>
       </c>
       <c r="R3" t="n">
-        <v>6831598</v>
+        <v>6831512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>130041507</v>
       </c>
       <c r="B4" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041545</v>
+        <v>130041431</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475757</v>
+        <v>475759</v>
       </c>
       <c r="R5" t="n">
-        <v>6831512</v>
+        <v>6831598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>130041550</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130041549</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041445</v>
+        <v>130041551</v>
       </c>
       <c r="B8" t="n">
-        <v>79127</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475693</v>
+        <v>475733</v>
       </c>
       <c r="R8" t="n">
-        <v>6831717</v>
+        <v>6831737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041551</v>
+        <v>130041547</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475733</v>
+        <v>475696</v>
       </c>
       <c r="R9" t="n">
-        <v>6831737</v>
+        <v>6831636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041547</v>
+        <v>130041445</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475696</v>
+        <v>475693</v>
       </c>
       <c r="R10" t="n">
-        <v>6831636</v>
+        <v>6831717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
         <v>130041546</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130041552</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041444</v>
+        <v>130041556</v>
       </c>
       <c r="B13" t="n">
-        <v>79127</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475670</v>
+        <v>475656</v>
       </c>
       <c r="R13" t="n">
-        <v>6831719</v>
+        <v>6831611</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041556</v>
+        <v>130041444</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475656</v>
+        <v>475670</v>
       </c>
       <c r="R14" t="n">
-        <v>6831611</v>
+        <v>6831719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>130041434</v>
       </c>
       <c r="B15" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041479</v>
+        <v>130041491</v>
       </c>
       <c r="B16" t="n">
-        <v>79119</v>
+        <v>78938</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475670</v>
+        <v>475660</v>
       </c>
       <c r="R16" t="n">
-        <v>6831652</v>
+        <v>6831683</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041491</v>
+        <v>130041479</v>
       </c>
       <c r="B17" t="n">
-        <v>78853</v>
+        <v>79204</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475660</v>
+        <v>475670</v>
       </c>
       <c r="R17" t="n">
-        <v>6831683</v>
+        <v>6831652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>130041490</v>
       </c>
       <c r="B18" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130041548</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>130044577</v>
       </c>
       <c r="B20" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>130044578</v>
       </c>
       <c r="B21" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>130044580</v>
       </c>
       <c r="B22" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129996509</v>
+        <v>130041444</v>
       </c>
       <c r="B2" t="n">
-        <v>78938</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Örnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475663</v>
+        <v>475670</v>
       </c>
       <c r="R2" t="n">
-        <v>6831687</v>
+        <v>6831719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130041545</v>
+        <v>130041445</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475757</v>
+        <v>475693</v>
       </c>
       <c r="R3" t="n">
-        <v>6831512</v>
+        <v>6831717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041507</v>
+        <v>130041545</v>
       </c>
       <c r="B4" t="n">
-        <v>78937</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475660</v>
+        <v>475757</v>
       </c>
       <c r="R4" t="n">
-        <v>6831685</v>
+        <v>6831512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041431</v>
+        <v>130041546</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475759</v>
+        <v>475705</v>
       </c>
       <c r="R5" t="n">
-        <v>6831598</v>
+        <v>6831611</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041550</v>
+        <v>130041547</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475670</v>
+        <v>475696</v>
       </c>
       <c r="R6" t="n">
-        <v>6831719</v>
+        <v>6831636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041549</v>
+        <v>130041548</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475670</v>
+        <v>475672</v>
       </c>
       <c r="R7" t="n">
-        <v>6831652</v>
+        <v>6831646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041445</v>
+        <v>130041549</v>
       </c>
       <c r="B8" t="n">
-        <v>79212</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475693</v>
+        <v>475670</v>
       </c>
       <c r="R8" t="n">
-        <v>6831717</v>
+        <v>6831652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041551</v>
+        <v>130041550</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475733</v>
+        <v>475670</v>
       </c>
       <c r="R9" t="n">
-        <v>6831737</v>
+        <v>6831719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041547</v>
+        <v>130041551</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475696</v>
+        <v>475733</v>
       </c>
       <c r="R10" t="n">
-        <v>6831636</v>
+        <v>6831737</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041546</v>
+        <v>130041552</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475705</v>
+        <v>475809</v>
       </c>
       <c r="R11" t="n">
-        <v>6831611</v>
+        <v>6831753</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041552</v>
+        <v>130041555</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475809</v>
+        <v>475668</v>
       </c>
       <c r="R12" t="n">
-        <v>6831753</v>
+        <v>6831734</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041444</v>
+        <v>130041556</v>
       </c>
       <c r="B13" t="n">
-        <v>79212</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475670</v>
+        <v>475656</v>
       </c>
       <c r="R13" t="n">
-        <v>6831719</v>
+        <v>6831611</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041556</v>
+        <v>130041479</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475656</v>
+        <v>475670</v>
       </c>
       <c r="R14" t="n">
-        <v>6831611</v>
+        <v>6831652</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041434</v>
+        <v>130041485</v>
       </c>
       <c r="B15" t="n">
-        <v>79799</v>
+        <v>79351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475658</v>
+        <v>475748</v>
       </c>
       <c r="R15" t="n">
-        <v>6831667</v>
+        <v>6831417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041479</v>
+        <v>130041507</v>
       </c>
       <c r="B16" t="n">
-        <v>79204</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475670</v>
+        <v>475660</v>
       </c>
       <c r="R16" t="n">
-        <v>6831652</v>
+        <v>6831685</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041491</v>
+        <v>130041431</v>
       </c>
       <c r="B17" t="n">
-        <v>78938</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475660</v>
+        <v>475759</v>
       </c>
       <c r="R17" t="n">
-        <v>6831683</v>
+        <v>6831598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041490</v>
+        <v>130041433</v>
       </c>
       <c r="B18" t="n">
-        <v>78938</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475696</v>
+        <v>475731</v>
       </c>
       <c r="R18" t="n">
-        <v>6831627</v>
+        <v>6831608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041548</v>
+        <v>130041434</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475672</v>
+        <v>475658</v>
       </c>
       <c r="R19" t="n">
-        <v>6831646</v>
+        <v>6831667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130044577</v>
+        <v>130044580</v>
       </c>
       <c r="B20" t="n">
-        <v>78938</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130044578</v>
+        <v>130041460</v>
       </c>
       <c r="B21" t="n">
-        <v>79770</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,37 +2713,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475722</v>
+        <v>475693</v>
       </c>
       <c r="R21" t="n">
-        <v>6831725</v>
+        <v>6831533</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,40 +2778,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130044580</v>
+        <v>129996509</v>
       </c>
       <c r="B22" t="n">
-        <v>79799</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,37 +2828,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475722</v>
+        <v>475663</v>
       </c>
       <c r="R22" t="n">
-        <v>6831725</v>
+        <v>6831687</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,12 +2882,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2885,22 +2906,437 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130041490</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>475696</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6831627</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130041491</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örnbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>475660</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6831683</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130044577</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>475722</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831725</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130044578</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>475722</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6831725</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53691-2025 artfynd.xlsx
+++ b/artfynd/A 53691-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041444</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041445</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041545</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041546</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041547</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041548</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041549</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041552</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041555</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041556</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041479</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041485</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041507</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041431</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041433</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041434</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2699,6 +2794,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044580</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2814,6 +2914,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041460</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2921,6 +3026,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996509</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3028,6 +3138,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041490</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3135,6 +3250,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041491</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3236,6 +3356,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044577</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,8 +3462,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>